--- a/experiments/experiment-1/mvc_block.xlsx
+++ b/experiments/experiment-1/mvc_block.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maik Bieleke\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhD-s\Repositories\psychopy-apparatus\psychopy-apparatus\experiments\experiment-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A10009-7ED0-43C6-A9E3-F27827382833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4234A6D-46E8-4C21-92CB-CFE090CDD0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="2304" windowWidth="19536" windowHeight="16488" xr2:uid="{3C72E597-D4FB-469B-AEF7-42009E7D3B97}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{3C72E597-D4FB-469B-AEF7-42009E7D3B97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -423,14 +423,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6BB6DD-CE65-42DD-8B3E-028BC7E3E3D2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.76953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.31640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -441,7 +441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -452,12 +452,12 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>45</v>
